--- a/experiment_results/wedos_grid/rtt_bursts_S2_atk5pct_wu300000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S2_atk5pct_wu300000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>76021</t>
+          <t>37588</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>86843</t>
+          <t>49270</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>99374</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>106664</t>
+          <t>56560</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>116268</t>
+          <t>59723</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>113080</t>
+          <t>53372</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>112871</t>
+          <t>59514</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>113896</t>
+          <t>54398</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>111801</t>
+          <t>57418</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>119131</t>
+          <t>61728</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>130447</t>
+          <t>68735</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>137058</t>
+          <t>68338</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>141715</t>
+          <t>73392</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>136570</t>
+          <t>63193</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>115557</t>
+          <t>52379</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>104743</t>
+          <t>52379</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
